--- a/output/Tables/2019/Monte Carlo/soc_1€_step_km_min_1000replicate.xlsx
+++ b/output/Tables/2019/Monte Carlo/soc_1€_step_km_min_1000replicate.xlsx
@@ -408,31 +408,31 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>170.7030078234056</v>
+        <v>270.9845007065639</v>
       </c>
       <c r="B2">
-        <v>177.0889279151407</v>
+        <v>279.5261935736585</v>
       </c>
       <c r="C2">
-        <v>184.5965233121353</v>
+        <v>289.4814890039606</v>
       </c>
       <c r="D2">
-        <v>0.1220526505937353</v>
+        <v>0.1937539180051937</v>
       </c>
       <c r="E2">
-        <v>0.126618583459326</v>
+        <v>0.1998612284051663</v>
       </c>
       <c r="F2">
-        <v>0.1319865141681771</v>
+        <v>0.2069792646378324</v>
       </c>
       <c r="G2">
-        <v>1.525658132421692</v>
+        <v>2.421923975064922</v>
       </c>
       <c r="H2">
-        <v>1.582732293241575</v>
+        <v>2.498265355064579</v>
       </c>
       <c r="I2">
-        <v>1.649831427102214</v>
+        <v>2.587240807972905</v>
       </c>
       <c r="J2">
         <v>1</v>

--- a/output/Tables/2019/Monte Carlo/soc_1€_step_km_min_1000replicate.xlsx
+++ b/output/Tables/2019/Monte Carlo/soc_1€_step_km_min_1000replicate.xlsx
@@ -408,31 +408,31 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>270.9845007065639</v>
+        <v>262.3275912296903</v>
       </c>
       <c r="B2">
-        <v>279.5261935736585</v>
+        <v>270.8291604878166</v>
       </c>
       <c r="C2">
-        <v>289.4814890039606</v>
+        <v>280.75625694296</v>
       </c>
       <c r="D2">
-        <v>0.1937539180051937</v>
+        <v>0.1875642277292291</v>
       </c>
       <c r="E2">
-        <v>0.1998612284051663</v>
+        <v>0.1936428497487894</v>
       </c>
       <c r="F2">
-        <v>0.2069792646378324</v>
+        <v>0.2007407237142169</v>
       </c>
       <c r="G2">
-        <v>2.421923975064922</v>
+        <v>2.344552846615364</v>
       </c>
       <c r="H2">
-        <v>2.498265355064579</v>
+        <v>2.420535621859867</v>
       </c>
       <c r="I2">
-        <v>2.587240807972905</v>
+        <v>2.509259046427712</v>
       </c>
       <c r="J2">
         <v>1</v>
